--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260903.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260903.xlsx
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1,281,332</t>
+          <t>8,567,484</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>8,567,484</t>
+          <t>1,281,332</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>7,991,198</t>
+          <t>4,158,238</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>4,158,238</t>
+          <t>7,991,198</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>202609TX</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>臺股期貨</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>4,983,126</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>202609TX</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>臺股期貨</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>4,983,126</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
